--- a/nr-update-Organization-type/ig/StructureDefinition-as-dp-organization.xlsx
+++ b/nr-update-Organization-type/ig/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T14:31:58+00:00</t>
+    <t>2024-02-19T14:41:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -23740,7 +23740,7 @@
         <v>81</v>
       </c>
       <c r="H204" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I204" t="s" s="2">
         <v>73</v>

--- a/nr-update-Organization-type/ig/StructureDefinition-as-dp-organization.xlsx
+++ b/nr-update-Organization-type/ig/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T14:41:57+00:00</t>
+    <t>2024-02-20T16:47:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-Organization-type/ig/StructureDefinition-as-dp-organization.xlsx
+++ b/nr-update-Organization-type/ig/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-20T16:47:04+00:00</t>
+    <t>2024-02-26T16:15:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
